--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,6 +974,49 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>signal_relay</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>building.signal_relay.desc</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,11 @@
           <t>unlockHintKey</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -529,6 +534,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -584,6 +594,11 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>未解锁时的解锁条件文本键(fg.TbLocText)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>建造菜单分类(fg.TbBuildCategory.id,FG3-LOG-01)</t>
         </is>
       </c>
     </row>
@@ -629,6 +644,11 @@
           <t>grid.unlock.always</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>signal</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -672,6 +692,11 @@
           <t>grid.unlock.always</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -715,6 +740,11 @@
           <t>grid.unlock.always</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -758,6 +788,11 @@
           <t>grid.unlock.always</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -801,6 +836,11 @@
           <t>grid.unlock.always</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>signal</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -844,6 +884,11 @@
           <t>grid.unlock.always</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -887,6 +932,11 @@
           <t>grid.unlock.always</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -930,6 +980,11 @@
           <t>grid.unlock.always</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -973,6 +1028,11 @@
           <t>grid.unlock.beacon</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>endgame</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1014,6 +1074,11 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>signal</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,6 +1082,102 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>power_pole</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>building.power_pole.desc</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>power_pole_t2</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>building.power_pole_t2.desc</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1178,6 +1178,342 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>recycler</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ruin</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>building.recycler.desc</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>gathering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>extraction_drill</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ore_metal|ore_rare</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>building.extraction_drill.desc</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>gathering</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>refinery_furnace</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>building.refinery_furnace.desc</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>refinery_tower</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>building.refinery_tower.desc</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>blending_station</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>building.blending_station.desc</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>waste_pond</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>building.waste_pond.desc</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>fluid_pump</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>water|oil</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>building.fluid_pump.desc</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>gathering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1514,6 +1514,198 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>parts_workshop</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>building.parts_workshop.desc</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>electronics_bench</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>building.electronics_bench.desc</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>component_workshop</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>building.component_workshop.desc</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>firmware_burner</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>building.firmware_burner.desc</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>manufacturing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1706,6 +1706,150 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>fuel_generator</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>building.fuel_generator.desc</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>solar_array</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>building.solar_array.desc</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>energy_storage</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>building.energy_storage.desc</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1850,6 +1850,54 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>override_array</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>research:signal.override_t1</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>building.override_array.desc</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>research.hint.override_t1</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>signal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:energy.pole_t2</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.energy.pole_t2</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:industry.refinery_tower</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.industry.refinery_tower</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:industry.electronics</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.industry.electronics</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:industry.components</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.industry.components</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:energy.fuel_generator</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.energy.fuel_generator</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:energy.solar</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.energy.solar</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:energy.storage</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.energy.storage</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -1889,12 +1889,60 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>research.hint.override_t1</t>
+          <t>research.hint.signal.override_t1</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sim_lab</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>building.sim_lab.desc</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>research</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1946,6 +1946,54 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>test_range</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>building.test_range.desc</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1994,6 +1994,54 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>circuit_synth</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>building.circuit_synth.desc</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>manufacturing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2042,6 +2042,54 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>listening_post</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>research:signal.listening_post</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>building.listening_post.desc</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>research.hint.signal.listening_post</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>intel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2090,6 +2090,54 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>blackbox_gallery</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>building.blackbox_gallery.desc</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2138,6 +2138,102 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>turret_light</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>building.turret_light.desc</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>turret_heavy</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>building.turret_heavy.desc</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2234,6 +2234,294 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>barrier_t1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>research:defense.barrier</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>building.barrier_t1.desc</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>research.hint.defense.barrier</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>barrier_t2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>research:defense.barrier</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>building.barrier_t2.desc</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>research.hint.defense.barrier</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>barrier_t3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>research:defense.barrier</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>building.barrier_t3.desc</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>research.hint.defense.barrier</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>gate</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>research:defense.barrier</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>building.gate.desc</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>research.hint.defense.barrier</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>shield_gen</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>research:defense.shield</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>building.shield_gen.desc</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>research.hint.defense.shield</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trap_emitter</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>research:defense.trap</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>building.trap_emitter.desc</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>research.hint.defense.trap</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2522,6 +2522,54 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>repair_drone_station</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>research:defense.repair_drone</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>building.repair_drone_station.desc</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>research.hint.defense.repair_drone</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2142,14 +2142,14 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>turret_light</t>
+          <t>purifier</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>building.turret_light.desc</t>
+          <t>building.purifier.desc</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>environment</t>
         </is>
       </c>
     </row>
@@ -2190,14 +2190,14 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>turret_heavy</t>
+          <t>turret_light</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>building.turret_heavy.desc</t>
+          <t>building.turret_light.desc</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2238,14 +2238,14 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>barrier_t1</t>
+          <t>turret_heavy</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>research:defense.barrier</t>
+          <t>always</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>building.barrier_t1.desc</t>
+          <t>building.turret_heavy.desc</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>research.hint.defense.barrier</t>
+          <t>grid.unlock.always</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2286,7 +2286,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>barrier_t2</t>
+          <t>barrier_t1</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>building.barrier_t2.desc</t>
+          <t>building.barrier_t1.desc</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2334,7 +2334,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>barrier_t3</t>
+          <t>barrier_t2</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>building.barrier_t3.desc</t>
+          <t>building.barrier_t2.desc</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2382,7 +2382,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>gate</t>
+          <t>barrier_t3</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>building.gate.desc</t>
+          <t>building.barrier_t3.desc</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2430,14 +2430,14 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>shield_gen</t>
+          <t>gate</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>research:defense.shield</t>
+          <t>research:defense.barrier</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>building.shield_gen.desc</t>
+          <t>building.gate.desc</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>research.hint.defense.shield</t>
+          <t>research.hint.defense.barrier</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2478,14 +2478,14 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>trap_emitter</t>
+          <t>shield_gen</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>research:defense.trap</t>
+          <t>research:defense.shield</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>building.trap_emitter.desc</t>
+          <t>building.shield_gen.desc</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>research.hint.defense.trap</t>
+          <t>research.hint.defense.shield</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2526,45 +2526,93 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
+          <t>trap_emitter</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>research:defense.trap</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>building.trap_emitter.desc</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>research.hint.defense.trap</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>repair_drone_station</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>3</v>
-      </c>
-      <c r="D44" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>research:defense.repair_drone</t>
         </is>
       </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>any</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>building.repair_drone_station.desc</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>research.hint.defense.repair_drone</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>defense</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingGrid-建筑格网属性.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2618,6 +2618,54 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>drop_station</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>research:expedition.drop_station</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>building.drop_station.desc</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>research.hint.expedition.drop_station</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
